--- a/AAII_Financials/Yearly/NWL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NWL_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
   <si>
     <t>NWL</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8133000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9459000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10589000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9385000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9714900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10154000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9552000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9181100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5915700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5727000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5607000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5579900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5511700</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5694000</v>
+      </c>
+      <c r="E9" s="3">
         <v>6603000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>14497000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6306000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6495500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6636300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6289000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15075400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3611100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3523600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3482100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7114800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3410600</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2439000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2856000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-3908000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3079000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3219400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3517700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3263000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-5894300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2304600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2203400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2124900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-1534900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2101100</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E12" s="3">
         <v>140000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>153000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>144000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>149000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>151000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>158000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>147000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>112600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>107500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>102900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>116100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>118500</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,51 +960,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>661000</v>
+      </c>
+      <c r="E14" s="3">
         <v>378000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>107000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1544000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1278400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>12323200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>201800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>112500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>302000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>151400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>110300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>98300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>408000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>8343000</v>
+      </c>
+      <c r="E17" s="3">
         <v>9012000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9577000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10039000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10224900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17712100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9198800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8930600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5487000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5155500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4991900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4950800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5203500</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-210000</v>
+      </c>
+      <c r="E18" s="3">
         <v>447000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1012000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-654000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-510000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7558100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>353200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>250500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>428700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>571500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>615100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>629100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>308200</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1146,92 +1178,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-333000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-290000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-252000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-352000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-341600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-433600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>239200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>166600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-31700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-60600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-11300</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-209000</v>
+      </c>
+      <c r="E21" s="3">
         <v>453000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1085000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-649000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-405600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7557800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1228000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>854300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>605900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>695900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>713400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>798400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>458500</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1253,111 +1292,120 @@
       <c r="I22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K22" s="3">
         <v>398300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>96800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>77700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>80400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>88400</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-543000</v>
+      </c>
+      <c r="E23" s="3">
         <v>157000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>760000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1006000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-851600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7991700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>592400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>18800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>337500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>462100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>536300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>554300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>208500</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-155000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-40000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>138000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-236000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1037700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1358900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-186200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>57100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>78200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>89100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>120000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>162300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>21300</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-388000</v>
+      </c>
+      <c r="E26" s="3">
         <v>197000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>622000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-770000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>186100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6632800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>778600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-38300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>259300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>373000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>416300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>392000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>187200</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-388000</v>
+      </c>
+      <c r="E27" s="3">
         <v>197000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>622000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-770000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>186100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6632800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>778600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-38300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>259400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>373100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>416400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>392100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>187300</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1523,51 +1580,57 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-79500</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-55700</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>1970200</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>566700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>90700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>4800</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>58300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>9300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-71400</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>333000</v>
+      </c>
+      <c r="E32" s="3">
         <v>290000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>252000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>352000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>341600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>433600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-239200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-166600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>31700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>60600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>11300</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-388000</v>
+      </c>
+      <c r="E33" s="3">
         <v>197000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>622000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-770000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>106600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6688500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2748800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>528400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>350100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>377900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>474700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>401400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>115900</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-388000</v>
+      </c>
+      <c r="E35" s="3">
         <v>197000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>622000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-770000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>106600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6688500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2748800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>528400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>350100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>377900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>474700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>401400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>115900</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>332000</v>
+      </c>
+      <c r="E41" s="3">
         <v>287000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>440000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>981000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>348600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>495700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>485700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>587500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>274800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>199400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>226300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>183800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>170200</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1984,177 +2073,192 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1195000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1250000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1500000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1678000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1841500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4219000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3758600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2746900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2501400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2496400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1105100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1112400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1002000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1531000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2203000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2087000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1638000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1606700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1760700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1662400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2116000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>721800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>708500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>684400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>696400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>699900</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>296000</v>
+      </c>
+      <c r="E45" s="3">
         <v>312000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>325000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>331000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>313100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1538600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7113800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2034100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>246200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>270500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>269800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>278500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>275900</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>3354000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4052000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4352000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4628000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4109900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5958500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10725700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7484500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2493500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2426600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2285600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2271100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2148000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2194,93 +2298,102 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>1762000</v>
+        <v>1727000</v>
       </c>
       <c r="E48" s="3">
         <v>1762000</v>
       </c>
       <c r="F48" s="3">
+        <v>1762000</v>
+      </c>
+      <c r="G48" s="3">
         <v>1706000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1770100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1226100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2495400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1543400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1198400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1118200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>539600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>560200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>551400</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>5559000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5947000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6874000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7117000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8625200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12994700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>23945600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>24330700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4918600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4320400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2975600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3024300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3032100</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>1523000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1501000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1281000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1249000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1136800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>513300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4767500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>478900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>311900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>262200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>268900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>366400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>429400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>12163000</v>
+      </c>
+      <c r="E54" s="3">
         <v>13262000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14269000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14700000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15642000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17722400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33135500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33837500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7221000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6681100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6069700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6222000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6160900</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1003000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1062000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1680000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1526000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1101400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1191600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1226800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1518900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>642400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>674100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>558900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>527400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>468500</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>329000</v>
+      </c>
+      <c r="E58" s="3">
         <v>621000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>466000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>332400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>318700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>661800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>601900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>394700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>397400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>174800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>211900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>367500</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>1565000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1395000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1634000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1629000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1544200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1798100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3206100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2171200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>957400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>819200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>870800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>831500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>824900</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2897000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3078000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3317000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3621000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2978000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3303500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4907700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4292000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1988600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1890700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1604500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1570800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1660900</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>4575000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4756000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4883000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5141000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5391300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6696300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9889200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11290900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2669100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2084500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1661600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1706500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1809300</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>1579000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1909000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1911000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2038000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2276700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2469400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5355600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6870200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>736900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>851000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>728600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>944500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>838100</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>9051000</v>
+      </c>
+      <c r="E66" s="3">
         <v>9743000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10111000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10826000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10678700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12504000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18990800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>22488700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5398100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4829700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3998200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4225300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4311800</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-2726000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2338000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2535000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3174000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2404200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2511300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4611200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2289900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2090900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2111200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2242100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2294900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2097300</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>3112000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3519000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4158000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3874000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4963300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5218400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14144700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11348800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1822900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1851400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2071500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1996700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1849100</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-388000</v>
+      </c>
+      <c r="E81" s="3">
         <v>197000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>622000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-770000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>106600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6688500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2748800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>528400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>350100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>377900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>474700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>401400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>115900</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>334000</v>
+      </c>
+      <c r="E83" s="3">
         <v>296000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>325000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>357000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>446000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>433900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>635600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>437200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>171600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>156100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>158900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>163700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>161600</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>930000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-272000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>884000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1432000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1044000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>680000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>966200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1840400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>592900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>634100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>605200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>618500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>561300</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-284000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-312000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-289000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-259000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-264900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-384400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-406200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-441400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-211400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-161900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-138200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-177200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-222900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-199000</v>
+      </c>
+      <c r="E94" s="3">
         <v>343000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-268000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-228000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>735400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>4807400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1078500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8824800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-649900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-751900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>53400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-163000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-206400</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>-184000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-385000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-394000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-392000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-390300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-434600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-428600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-328600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-206300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-182500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-174100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-125900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-84900</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-664000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-232000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1143000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-559000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1903600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5454500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2195800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>7328500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>145200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>119000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-613500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-446000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-324600</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-13000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-17000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-22900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>49300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-31400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-12800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-28100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-174000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-544000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>650000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-124800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-101800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>312700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>75400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-26900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>42500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>30600</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NWL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NWL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
   <si>
     <t>NWL</t>
   </si>
@@ -738,13 +738,13 @@
         <v>9385000</v>
       </c>
       <c r="H8" s="3">
-        <v>9714900</v>
+        <v>9715000</v>
       </c>
       <c r="I8" s="3">
         <v>10154000</v>
       </c>
       <c r="J8" s="3">
-        <v>9552000</v>
+        <v>11170400</v>
       </c>
       <c r="K8" s="3">
         <v>9181100</v>
@@ -777,19 +777,19 @@
         <v>6603000</v>
       </c>
       <c r="F9" s="3">
-        <v>14497000</v>
+        <v>7204000</v>
       </c>
       <c r="G9" s="3">
-        <v>6306000</v>
+        <v>6297000</v>
       </c>
       <c r="H9" s="3">
-        <v>6495500</v>
+        <v>6480000</v>
       </c>
       <c r="I9" s="3">
-        <v>6636300</v>
+        <v>6636000</v>
       </c>
       <c r="J9" s="3">
-        <v>6289000</v>
+        <v>7359900</v>
       </c>
       <c r="K9" s="3">
         <v>15075400</v>
@@ -822,19 +822,19 @@
         <v>2856000</v>
       </c>
       <c r="F10" s="3">
-        <v>-3908000</v>
+        <v>3385000</v>
       </c>
       <c r="G10" s="3">
-        <v>3079000</v>
+        <v>3088000</v>
       </c>
       <c r="H10" s="3">
-        <v>3219400</v>
+        <v>3235000</v>
       </c>
       <c r="I10" s="3">
-        <v>3517700</v>
+        <v>3518000</v>
       </c>
       <c r="J10" s="3">
-        <v>3263000</v>
+        <v>3810500</v>
       </c>
       <c r="K10" s="3">
         <v>-5894300</v>
@@ -898,7 +898,7 @@
         <v>151000</v>
       </c>
       <c r="J12" s="3">
-        <v>158000</v>
+        <v>175000</v>
       </c>
       <c r="K12" s="3">
         <v>147000</v>
@@ -979,16 +979,16 @@
         <v>107000</v>
       </c>
       <c r="G14" s="3">
-        <v>1544000</v>
+        <v>1576000</v>
       </c>
       <c r="H14" s="3">
-        <v>1278400</v>
+        <v>1354000</v>
       </c>
       <c r="I14" s="3">
-        <v>12323200</v>
+        <v>8427000</v>
       </c>
       <c r="J14" s="3">
-        <v>201800</v>
+        <v>-500700</v>
       </c>
       <c r="K14" s="3">
         <v>112500</v>
@@ -1015,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>334000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>296000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>325000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>446000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>372000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>400200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>8343000</v>
+        <v>7687000</v>
       </c>
       <c r="E17" s="3">
-        <v>9012000</v>
+        <v>8633000</v>
       </c>
       <c r="F17" s="3">
-        <v>9577000</v>
+        <v>9468000</v>
       </c>
       <c r="G17" s="3">
-        <v>10039000</v>
+        <v>8520000</v>
       </c>
       <c r="H17" s="3">
-        <v>10224900</v>
+        <v>8893000</v>
       </c>
       <c r="I17" s="3">
-        <v>17712100</v>
+        <v>9267000</v>
       </c>
       <c r="J17" s="3">
-        <v>9198800</v>
+        <v>10272200</v>
       </c>
       <c r="K17" s="3">
         <v>8930600</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-210000</v>
+        <v>446000</v>
       </c>
       <c r="E18" s="3">
-        <v>447000</v>
+        <v>826000</v>
       </c>
       <c r="F18" s="3">
-        <v>1012000</v>
+        <v>1121000</v>
       </c>
       <c r="G18" s="3">
-        <v>-654000</v>
+        <v>865000</v>
       </c>
       <c r="H18" s="3">
-        <v>-510000</v>
+        <v>822000</v>
       </c>
       <c r="I18" s="3">
-        <v>-7558100</v>
+        <v>887000</v>
       </c>
       <c r="J18" s="3">
-        <v>353200</v>
+        <v>898200</v>
       </c>
       <c r="K18" s="3">
         <v>250500</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-333000</v>
+        <v>45000</v>
       </c>
       <c r="E20" s="3">
-        <v>-290000</v>
+        <v>56000</v>
       </c>
       <c r="F20" s="3">
-        <v>-252000</v>
+        <v>-2000</v>
       </c>
       <c r="G20" s="3">
-        <v>-352000</v>
+        <v>16000</v>
       </c>
       <c r="H20" s="3">
-        <v>-341600</v>
+        <v>17000</v>
       </c>
       <c r="I20" s="3">
-        <v>-433600</v>
+        <v>6000</v>
       </c>
       <c r="J20" s="3">
-        <v>239200</v>
+        <v>3800</v>
       </c>
       <c r="K20" s="3">
         <v>166600</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-209000</v>
+        <v>735000</v>
       </c>
       <c r="E21" s="3">
-        <v>453000</v>
+        <v>1066000</v>
       </c>
       <c r="F21" s="3">
-        <v>1085000</v>
+        <v>1448000</v>
       </c>
       <c r="G21" s="3">
-        <v>-649000</v>
+        <v>1206000</v>
       </c>
       <c r="H21" s="3">
-        <v>-405600</v>
+        <v>1251000</v>
       </c>
       <c r="I21" s="3">
-        <v>-7557800</v>
+        <v>1253000</v>
       </c>
       <c r="J21" s="3">
-        <v>1228000</v>
+        <v>1294600</v>
       </c>
       <c r="K21" s="3">
         <v>854300</v>
@@ -1274,26 +1274,26 @@
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>91</v>
+      <c r="D22" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>235000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>256000</v>
+      </c>
+      <c r="G22" s="3">
+        <v>274000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>303000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>446000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>475800</v>
       </c>
       <c r="K22" s="3">
         <v>398300</v>
@@ -1329,16 +1329,16 @@
         <v>760000</v>
       </c>
       <c r="G23" s="3">
-        <v>-1006000</v>
+        <v>-1001000</v>
       </c>
       <c r="H23" s="3">
-        <v>-851600</v>
+        <v>-852000</v>
       </c>
       <c r="I23" s="3">
-        <v>-7991700</v>
+        <v>-7992000</v>
       </c>
       <c r="J23" s="3">
-        <v>592400</v>
+        <v>919300</v>
       </c>
       <c r="K23" s="3">
         <v>18800</v>
@@ -1374,16 +1374,16 @@
         <v>138000</v>
       </c>
       <c r="G24" s="3">
-        <v>-236000</v>
+        <v>-235000</v>
       </c>
       <c r="H24" s="3">
-        <v>-1037700</v>
+        <v>-1038000</v>
       </c>
       <c r="I24" s="3">
-        <v>-1358900</v>
+        <v>-1359000</v>
       </c>
       <c r="J24" s="3">
-        <v>-186200</v>
+        <v>-1515000</v>
       </c>
       <c r="K24" s="3">
         <v>57100</v>
@@ -1464,16 +1464,16 @@
         <v>622000</v>
       </c>
       <c r="G26" s="3">
-        <v>-770000</v>
+        <v>-766000</v>
       </c>
       <c r="H26" s="3">
-        <v>186100</v>
+        <v>186000</v>
       </c>
       <c r="I26" s="3">
-        <v>-6632800</v>
+        <v>-6633000</v>
       </c>
       <c r="J26" s="3">
-        <v>778600</v>
+        <v>2434300</v>
       </c>
       <c r="K26" s="3">
         <v>-38300</v>
@@ -1509,16 +1509,16 @@
         <v>622000</v>
       </c>
       <c r="G27" s="3">
-        <v>-770000</v>
+        <v>-766000</v>
       </c>
       <c r="H27" s="3">
-        <v>186100</v>
+        <v>107000</v>
       </c>
       <c r="I27" s="3">
-        <v>-6632800</v>
+        <v>-6942000</v>
       </c>
       <c r="J27" s="3">
-        <v>778600</v>
+        <v>2748800</v>
       </c>
       <c r="K27" s="3">
         <v>-38300</v>
@@ -1589,11 +1589,11 @@
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>91</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1602,13 +1602,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-79500</v>
+        <v>-79000</v>
       </c>
       <c r="I29" s="3">
-        <v>-55700</v>
+        <v>-309000</v>
       </c>
       <c r="J29" s="3">
-        <v>1970200</v>
+        <v>314500</v>
       </c>
       <c r="K29" s="3">
         <v>566700</v>
@@ -1725,25 +1725,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>333000</v>
+        <v>-45000</v>
       </c>
       <c r="E32" s="3">
-        <v>290000</v>
+        <v>-56000</v>
       </c>
       <c r="F32" s="3">
-        <v>252000</v>
+        <v>2000</v>
       </c>
       <c r="G32" s="3">
-        <v>352000</v>
+        <v>-16000</v>
       </c>
       <c r="H32" s="3">
-        <v>341600</v>
+        <v>-17000</v>
       </c>
       <c r="I32" s="3">
-        <v>433600</v>
+        <v>-6000</v>
       </c>
       <c r="J32" s="3">
-        <v>-239200</v>
+        <v>-3800</v>
       </c>
       <c r="K32" s="3">
         <v>-166600</v>
@@ -1779,13 +1779,13 @@
         <v>622000</v>
       </c>
       <c r="G33" s="3">
-        <v>-770000</v>
+        <v>-766000</v>
       </c>
       <c r="H33" s="3">
-        <v>106600</v>
+        <v>107000</v>
       </c>
       <c r="I33" s="3">
-        <v>-6688500</v>
+        <v>-6942000</v>
       </c>
       <c r="J33" s="3">
         <v>2748800</v>
@@ -1869,13 +1869,13 @@
         <v>622000</v>
       </c>
       <c r="G35" s="3">
-        <v>-770000</v>
+        <v>-766000</v>
       </c>
       <c r="H35" s="3">
-        <v>106600</v>
+        <v>107000</v>
       </c>
       <c r="I35" s="3">
-        <v>-6688500</v>
+        <v>-6942000</v>
       </c>
       <c r="J35" s="3">
         <v>2748800</v>
@@ -2005,7 +2005,7 @@
         <v>981000</v>
       </c>
       <c r="H41" s="3">
-        <v>348600</v>
+        <v>349000</v>
       </c>
       <c r="I41" s="3">
         <v>495700</v>
@@ -2095,13 +2095,13 @@
         <v>1678000</v>
       </c>
       <c r="H43" s="3">
-        <v>1841500</v>
+        <v>1842000</v>
       </c>
       <c r="I43" s="3">
-        <v>4219000</v>
+        <v>2163500</v>
       </c>
       <c r="J43" s="3">
-        <v>3758600</v>
+        <v>1879300</v>
       </c>
       <c r="K43" s="3">
         <v>2746900</v>
@@ -2140,7 +2140,7 @@
         <v>1638000</v>
       </c>
       <c r="H44" s="3">
-        <v>1606700</v>
+        <v>1606000</v>
       </c>
       <c r="I44" s="3">
         <v>1760700</v>
@@ -2173,25 +2173,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>296000</v>
+        <v>30000</v>
       </c>
       <c r="E45" s="3">
-        <v>312000</v>
+        <v>62000</v>
       </c>
       <c r="F45" s="3">
-        <v>325000</v>
+        <v>37000</v>
       </c>
       <c r="G45" s="3">
-        <v>331000</v>
+        <v>21000</v>
       </c>
       <c r="H45" s="3">
-        <v>313100</v>
+        <v>11000</v>
       </c>
       <c r="I45" s="3">
-        <v>1538600</v>
+        <v>1243800</v>
       </c>
       <c r="J45" s="3">
-        <v>7113800</v>
+        <v>6370400</v>
       </c>
       <c r="K45" s="3">
         <v>2034100</v>
@@ -2230,7 +2230,7 @@
         <v>4628000</v>
       </c>
       <c r="H46" s="3">
-        <v>4109900</v>
+        <v>4110000</v>
       </c>
       <c r="I46" s="3">
         <v>5958500</v>
@@ -2262,26 +2262,26 @@
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>2000</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>1706000</v>
       </c>
       <c r="H48" s="3">
-        <v>1770100</v>
+        <v>1770000</v>
       </c>
       <c r="I48" s="3">
         <v>1226100</v>
       </c>
       <c r="J48" s="3">
-        <v>2495400</v>
+        <v>972400</v>
       </c>
       <c r="K48" s="3">
         <v>1543400</v>
@@ -2365,13 +2365,13 @@
         <v>7117000</v>
       </c>
       <c r="H49" s="3">
-        <v>8625200</v>
+        <v>8625000</v>
       </c>
       <c r="I49" s="3">
-        <v>12994700</v>
+        <v>10024500</v>
       </c>
       <c r="J49" s="3">
-        <v>23945600</v>
+        <v>17072600</v>
       </c>
       <c r="K49" s="3">
         <v>24330700</v>
@@ -2488,25 +2488,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>1523000</v>
+        <v>717000</v>
       </c>
       <c r="E52" s="3">
-        <v>1501000</v>
+        <v>691000</v>
       </c>
       <c r="F52" s="3">
-        <v>1281000</v>
+        <v>464000</v>
       </c>
       <c r="G52" s="3">
-        <v>1249000</v>
+        <v>404000</v>
       </c>
       <c r="H52" s="3">
-        <v>1136800</v>
+        <v>359000</v>
       </c>
       <c r="I52" s="3">
-        <v>513300</v>
+        <v>330000</v>
       </c>
       <c r="J52" s="3">
-        <v>4767500</v>
+        <v>4220000</v>
       </c>
       <c r="K52" s="3">
         <v>478900</v>
@@ -2673,7 +2673,7 @@
         <v>1526000</v>
       </c>
       <c r="H57" s="3">
-        <v>1101400</v>
+        <v>1102000</v>
       </c>
       <c r="I57" s="3">
         <v>1191600</v>
@@ -2706,19 +2706,19 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>329000</v>
+        <v>466000</v>
       </c>
       <c r="E58" s="3">
-        <v>621000</v>
+        <v>756000</v>
       </c>
       <c r="F58" s="3">
-        <v>3000</v>
+        <v>125000</v>
       </c>
       <c r="G58" s="3">
-        <v>466000</v>
+        <v>595000</v>
       </c>
       <c r="H58" s="3">
-        <v>332400</v>
+        <v>465000</v>
       </c>
       <c r="I58" s="3">
         <v>318700</v>
@@ -2751,25 +2751,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>1565000</v>
+        <v>116000</v>
       </c>
       <c r="E59" s="3">
-        <v>1395000</v>
+        <v>72000</v>
       </c>
       <c r="F59" s="3">
-        <v>1634000</v>
+        <v>59000</v>
       </c>
       <c r="G59" s="3">
-        <v>1629000</v>
+        <v>102000</v>
       </c>
       <c r="H59" s="3">
-        <v>1544200</v>
+        <v>131000</v>
       </c>
       <c r="I59" s="3">
-        <v>1798100</v>
+        <v>458300</v>
       </c>
       <c r="J59" s="3">
-        <v>3206100</v>
+        <v>1909500</v>
       </c>
       <c r="K59" s="3">
         <v>2171200</v>
@@ -2841,19 +2841,19 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>4575000</v>
+        <v>5144000</v>
       </c>
       <c r="E61" s="3">
-        <v>4756000</v>
+        <v>5359000</v>
       </c>
       <c r="F61" s="3">
-        <v>4883000</v>
+        <v>5424000</v>
       </c>
       <c r="G61" s="3">
-        <v>5141000</v>
+        <v>5715000</v>
       </c>
       <c r="H61" s="3">
-        <v>5391300</v>
+        <v>5932000</v>
       </c>
       <c r="I61" s="3">
         <v>6696300</v>
@@ -2886,25 +2886,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>1579000</v>
+        <v>576000</v>
       </c>
       <c r="E62" s="3">
-        <v>1909000</v>
+        <v>589000</v>
       </c>
       <c r="F62" s="3">
-        <v>1911000</v>
+        <v>657000</v>
       </c>
       <c r="G62" s="3">
-        <v>2038000</v>
+        <v>679000</v>
       </c>
       <c r="H62" s="3">
-        <v>2276700</v>
+        <v>728000</v>
       </c>
       <c r="I62" s="3">
-        <v>2469400</v>
+        <v>981200</v>
       </c>
       <c r="J62" s="3">
-        <v>5355600</v>
+        <v>1150400</v>
       </c>
       <c r="K62" s="3">
         <v>6870200</v>
@@ -3075,16 +3075,16 @@
         <v>10111000</v>
       </c>
       <c r="G66" s="3">
-        <v>10826000</v>
+        <v>10800000</v>
       </c>
       <c r="H66" s="3">
-        <v>10678700</v>
+        <v>10646000</v>
       </c>
       <c r="I66" s="3">
-        <v>12504000</v>
+        <v>12469200</v>
       </c>
       <c r="J66" s="3">
-        <v>18990800</v>
+        <v>18954200</v>
       </c>
       <c r="K66" s="3">
         <v>22488700</v>
@@ -3322,7 +3322,7 @@
         <v>-3174000</v>
       </c>
       <c r="H72" s="3">
-        <v>-2404200</v>
+        <v>-2404000</v>
       </c>
       <c r="I72" s="3">
         <v>-2511300</v>
@@ -3502,7 +3502,7 @@
         <v>3874000</v>
       </c>
       <c r="H76" s="3">
-        <v>4963300</v>
+        <v>4963000</v>
       </c>
       <c r="I76" s="3">
         <v>5218400</v>
@@ -3639,13 +3639,13 @@
         <v>622000</v>
       </c>
       <c r="G81" s="3">
-        <v>-770000</v>
+        <v>-766000</v>
       </c>
       <c r="H81" s="3">
-        <v>106600</v>
+        <v>107000</v>
       </c>
       <c r="I81" s="3">
-        <v>-6688500</v>
+        <v>-6942000</v>
       </c>
       <c r="J81" s="3">
         <v>2748800</v>
@@ -3694,25 +3694,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>334000</v>
+        <v>225000</v>
       </c>
       <c r="E83" s="3">
-        <v>296000</v>
+        <v>196000</v>
       </c>
       <c r="F83" s="3">
-        <v>325000</v>
+        <v>205000</v>
       </c>
       <c r="G83" s="3">
-        <v>357000</v>
+        <v>200000</v>
       </c>
       <c r="H83" s="3">
-        <v>446000</v>
+        <v>254000</v>
       </c>
       <c r="I83" s="3">
-        <v>433900</v>
+        <v>183000</v>
       </c>
       <c r="J83" s="3">
-        <v>635600</v>
+        <v>196200</v>
       </c>
       <c r="K83" s="3">
         <v>437200</v>
@@ -4040,10 +4040,10 @@
         <v>-259000</v>
       </c>
       <c r="H91" s="3">
-        <v>-264900</v>
+        <v>-265000</v>
       </c>
       <c r="I91" s="3">
-        <v>-384400</v>
+        <v>-384000</v>
       </c>
       <c r="J91" s="3">
         <v>-406200</v>
@@ -4175,10 +4175,10 @@
         <v>-228000</v>
       </c>
       <c r="H94" s="3">
-        <v>735400</v>
+        <v>736000</v>
       </c>
       <c r="I94" s="3">
-        <v>4807400</v>
+        <v>4807000</v>
       </c>
       <c r="J94" s="3">
         <v>1078500</v>
@@ -4227,25 +4227,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-184000</v>
+        <v>184000</v>
       </c>
       <c r="E96" s="3">
-        <v>-385000</v>
+        <v>385000</v>
       </c>
       <c r="F96" s="3">
-        <v>-394000</v>
+        <v>394000</v>
       </c>
       <c r="G96" s="3">
-        <v>-392000</v>
+        <v>392000</v>
       </c>
       <c r="H96" s="3">
-        <v>-390300</v>
+        <v>391000</v>
       </c>
       <c r="I96" s="3">
-        <v>-434600</v>
+        <v>435000</v>
       </c>
       <c r="J96" s="3">
-        <v>-428600</v>
+        <v>428600</v>
       </c>
       <c r="K96" s="3">
         <v>-328600</v>
@@ -4419,10 +4419,10 @@
         <v>-559000</v>
       </c>
       <c r="H100" s="3">
-        <v>-1903600</v>
+        <v>-1904000</v>
       </c>
       <c r="I100" s="3">
-        <v>-5454500</v>
+        <v>-5454000</v>
       </c>
       <c r="J100" s="3">
         <v>-2195800</v>
@@ -4464,10 +4464,10 @@
         <v>5000</v>
       </c>
       <c r="H101" s="3">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
       <c r="I101" s="3">
-        <v>-22900</v>
+        <v>-23000</v>
       </c>
       <c r="J101" s="3">
         <v>49300</v>
@@ -4509,7 +4509,7 @@
         <v>650000</v>
       </c>
       <c r="H102" s="3">
-        <v>-124800</v>
+        <v>-125000</v>
       </c>
       <c r="I102" s="3">
         <v>10000</v>

--- a/AAII_Financials/Yearly/NWL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NWL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
   <si>
     <t>NWL</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7582000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8133000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9459000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10589000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9385000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9715000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10154000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11170400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9181100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5915700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5727000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5607000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5579900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5511700</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4998000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5694000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6603000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7204000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6297000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6480000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6636000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7359900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15075400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3611100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3523600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3482100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7114800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3410600</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2584000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2439000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2856000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3385000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3088000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3235000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3518000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3810500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-5894300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2304600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2203400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2124900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1534900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2101100</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E12" s="3">
         <v>117000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>140000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>153000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>144000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>149000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>151000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>175000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>147000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>112600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>107500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>102900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>116100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>118500</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,81 +979,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>661000</v>
+        <v>460000</v>
       </c>
       <c r="E14" s="3">
+        <v>662000</v>
+      </c>
+      <c r="F14" s="3">
         <v>378000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>107000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1576000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1354000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8427000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-500700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>112500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>302000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>151400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>110300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>98300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>408000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>323000</v>
+      </c>
+      <c r="E15" s="3">
         <v>334000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>296000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>325000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>357000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>446000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>372000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>400200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>7687000</v>
+        <v>7056000</v>
       </c>
       <c r="E17" s="3">
-        <v>8633000</v>
+        <v>7682000</v>
       </c>
       <c r="F17" s="3">
+        <v>8629000</v>
+      </c>
+      <c r="G17" s="3">
         <v>9468000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8520000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8893000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9267000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10272200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8930600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5487000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5155500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4991900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4950800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5203500</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>446000</v>
+        <v>526000</v>
       </c>
       <c r="E18" s="3">
-        <v>826000</v>
+        <v>451000</v>
       </c>
       <c r="F18" s="3">
+        <v>830000</v>
+      </c>
+      <c r="G18" s="3">
         <v>1121000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>865000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>822000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>887000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>898200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>250500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>428700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>571500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>615100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>629100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>308200</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>45000</v>
+        <v>31000</v>
       </c>
       <c r="E20" s="3">
-        <v>56000</v>
+        <v>49000</v>
       </c>
       <c r="F20" s="3">
+        <v>60000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>16000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>17000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>166600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-31700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-60600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>735000</v>
+        <v>818000</v>
       </c>
       <c r="E21" s="3">
+        <v>736000</v>
+      </c>
+      <c r="F21" s="3">
         <v>1066000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1448000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1206000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1251000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1253000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1294600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>854300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>605900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>695900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>713400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>798400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>458500</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>295000</v>
+      </c>
+      <c r="E22" s="3">
         <v>283000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>235000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>256000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>274000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>303000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>446000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>475800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>398300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>96800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>77700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>18200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>80400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>88400</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-260000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-543000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>157000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>760000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1001000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-852000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7992000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>919300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>18800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>337500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>462100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>536300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>554300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>208500</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-155000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-40000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>138000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-235000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1038000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1359000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1515000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>57100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>78200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>89100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>120000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>162300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>21300</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-216000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-388000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>197000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>622000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-766000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>186000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6633000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2434300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-38300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>259300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>373000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>416300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>392000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>187200</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-216000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-388000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>197000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>622000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-766000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>107000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6942000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2748800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-38300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>259400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>373100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>416400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>392100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>187300</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1602,35 +1662,38 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-79000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-309000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>314500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>566700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>90700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>4800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>58300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>9300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-71400</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-45000</v>
+        <v>-31000</v>
       </c>
       <c r="E32" s="3">
-        <v>-56000</v>
+        <v>-49000</v>
       </c>
       <c r="F32" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="G32" s="3">
         <v>2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-16000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-17000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-166600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>31700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>60600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>11300</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-216000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-388000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>197000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>622000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-766000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>107000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6942000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2748800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>528400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>350100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>377900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>474700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>401400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>115900</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-216000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-388000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>197000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>622000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-766000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>107000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6942000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2748800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>528400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>350100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>377900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>474700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>401400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>115900</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1987,53 +2072,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E41" s="3">
         <v>332000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>287000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>440000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>981000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>349000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>495700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>485700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>587500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>274800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>199400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>226300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>183800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>170200</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2076,189 +2165,204 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>878000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1195000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1250000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1500000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1678000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1842000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2163500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1879300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2746900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2501400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2496400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1105100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1112400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1002000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1400000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1531000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2203000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2087000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1638000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1606000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1760700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1662400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2116000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>721800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>708500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>684400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>696400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>699900</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E45" s="3">
         <v>30000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>62000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1243800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6370400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2034100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>246200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>270500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>269800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>278500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>275900</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>2775000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3354000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4052000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4352000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4628000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4110000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5958500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10725700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7484500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2493500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2426600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2285600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2271100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2148000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2268,23 +2372,23 @@
       <c r="E47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G47" s="3">
         <v>3000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2000</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2301,99 +2405,108 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>1623000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1727000</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1762000</v>
       </c>
       <c r="F48" s="3">
         <v>1762000</v>
       </c>
       <c r="G48" s="3">
+        <v>1762000</v>
+      </c>
+      <c r="H48" s="3">
         <v>1706000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1770000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1226100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>972400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1543400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1198400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1118200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>539600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>560200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>551400</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>5046000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5559000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5947000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6874000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7117000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8625000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10024500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17072600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>24330700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4918600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4320400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2975600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3024300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3032100</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>754000</v>
+      </c>
+      <c r="E52" s="3">
         <v>717000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>691000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>464000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>404000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>359000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>330000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4220000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>478900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>311900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>262200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>268900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>366400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>429400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>11004000</v>
+      </c>
+      <c r="E54" s="3">
         <v>12163000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13262000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14269000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14700000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15642000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17722400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33135500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33837500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7221000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6681100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6069700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6222000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6160900</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>891000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1003000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1062000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1680000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1526000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1102000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1191600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1226800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1518900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>642400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>674100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>558900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>527400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>468500</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>466000</v>
+        <v>197000</v>
       </c>
       <c r="E58" s="3">
-        <v>756000</v>
+        <v>451000</v>
       </c>
       <c r="F58" s="3">
+        <v>742000</v>
+      </c>
+      <c r="G58" s="3">
         <v>125000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>595000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>465000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>318700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>661800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>601900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>394700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>397400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>174800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>211900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>367500</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>116000</v>
+        <v>88000</v>
       </c>
       <c r="E59" s="3">
-        <v>72000</v>
+        <v>89000</v>
       </c>
       <c r="F59" s="3">
+        <v>53000</v>
+      </c>
+      <c r="G59" s="3">
         <v>59000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>102000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>131000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>458300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1909500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2171200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>957400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>819200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>870800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>831500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>824900</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2437000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2897000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3078000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3317000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3621000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2978000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3303500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4907700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4292000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1988600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1890700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1604500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1570800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1660900</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>4990000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5144000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5359000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5424000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5715000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5932000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6696300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9889200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11290900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2669100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2084500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1661600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1706500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1809300</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E62" s="3">
         <v>576000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>589000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>657000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>679000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>728000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>981200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1150400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6870200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>736900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>851000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>728600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>944500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>838100</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>8253000</v>
+      </c>
+      <c r="E66" s="3">
         <v>9051000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9743000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10111000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10800000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10646000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12469200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>18954200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>22488700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5398100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4829700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3998200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4225300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4311800</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-2942000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2726000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2338000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2535000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3174000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2404000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2511300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4611200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2289900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2090900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2111200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2242100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2294900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2097300</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>2751000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3112000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3519000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4158000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3874000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4963000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5218400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14144700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11348800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1822900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1851400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2071500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1996700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1849100</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-216000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-388000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>197000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>622000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-766000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>107000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6942000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2748800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>528400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>350100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>377900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>474700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>401400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>115900</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E83" s="3">
         <v>225000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>196000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>205000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>254000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>183000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>196200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>437200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>171600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>156100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>158900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>163700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>161600</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>496000</v>
+      </c>
+      <c r="E89" s="3">
         <v>930000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-272000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>884000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1432000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1044000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>680000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>966200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1840400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>592900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>634100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>605200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>618500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>561300</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-259000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-284000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-312000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-289000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-259000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-265000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-384000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-406200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-441400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-211400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-161900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-138200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-177200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-222900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-151000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-199000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>343000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-268000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-228000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>736000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4807000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1078500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8824800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-649900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-751900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>53400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-163000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-206400</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E96" s="3">
         <v>184000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>385000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>394000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>392000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>391000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>435000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>428600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-328600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-206300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-182500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-174100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-125900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-451000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-664000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-232000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1143000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-559000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1904000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5454000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2195800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7328500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>145200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>119000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-613500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-446000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-324600</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-9000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-13000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-17000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>5000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-23000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>49300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-31400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-12800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-28100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-142000</v>
+      </c>
+      <c r="E102" s="3">
         <v>58000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-174000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-544000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>650000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-125000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-101800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>312700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>75400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-26900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>42500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>13600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>30600</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NWL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NWL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
   <si>
     <t>NWL</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7204000</v>
+      </c>
+      <c r="E8" s="3">
         <v>7582000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8133000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9459000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10589000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9385000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9715000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10154000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11170400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9181100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5915700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5727000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5607000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5579900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5511700</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4768000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4998000</v>
       </c>
-      <c r="E9" s="3">
-        <v>5694000</v>
-      </c>
       <c r="F9" s="3">
+        <v>5780000</v>
+      </c>
+      <c r="G9" s="3">
         <v>6603000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7204000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6297000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6480000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6636000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7359900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15075400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3611100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3523600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3482100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7114800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3410600</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2436000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2584000</v>
       </c>
-      <c r="E10" s="3">
-        <v>2439000</v>
-      </c>
       <c r="F10" s="3">
+        <v>2353000</v>
+      </c>
+      <c r="G10" s="3">
         <v>2856000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3385000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3088000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3235000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3518000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3810500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-5894300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2304600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2203400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2124900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-1534900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2101100</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,56 +899,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E12" s="3">
         <v>123000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>117000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>140000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>153000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>144000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>149000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>151000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>175000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>147000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>112600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>107500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>102900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>116100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>118500</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,87 +998,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>460000</v>
+        <v>437000</v>
       </c>
       <c r="E14" s="3">
-        <v>662000</v>
+        <v>462000</v>
       </c>
       <c r="F14" s="3">
+        <v>563000</v>
+      </c>
+      <c r="G14" s="3">
         <v>378000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>107000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1576000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1354000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8427000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-500700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>112500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>302000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>151400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>110300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>98300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>408000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>311000</v>
+      </c>
+      <c r="E15" s="3">
         <v>323000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>334000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>296000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>325000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>357000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>446000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>372000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>400200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>6716000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7056000</v>
       </c>
-      <c r="E17" s="3">
-        <v>7682000</v>
-      </c>
       <c r="F17" s="3">
+        <v>7781000</v>
+      </c>
+      <c r="G17" s="3">
         <v>8629000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9468000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8520000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8893000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9267000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10272200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8930600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5487000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5155500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4991900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4950800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5203500</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>488000</v>
+      </c>
+      <c r="E18" s="3">
         <v>526000</v>
       </c>
-      <c r="E18" s="3">
-        <v>451000</v>
-      </c>
       <c r="F18" s="3">
+        <v>352000</v>
+      </c>
+      <c r="G18" s="3">
         <v>830000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1121000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>865000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>822000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>887000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>898200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>250500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>428700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>571500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>615100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>629100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>308200</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1212,8 +1244,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1221,239 +1254,254 @@
         <v>31000</v>
       </c>
       <c r="E20" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F20" s="3">
         <v>49000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>60000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>16000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>17000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>166600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-31700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-60600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-11300</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>818000</v>
+        <v>768000</v>
       </c>
       <c r="E21" s="3">
-        <v>736000</v>
+        <v>820000</v>
       </c>
       <c r="F21" s="3">
+        <v>637000</v>
+      </c>
+      <c r="G21" s="3">
         <v>1066000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1448000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1206000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1251000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1253000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1294600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>854300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>605900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>695900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>713400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>798400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>458500</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>321000</v>
+      </c>
+      <c r="E22" s="3">
         <v>295000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>283000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>235000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>256000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>274000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>303000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>446000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>475800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>398300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>96800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>77700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>18200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>80400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>88400</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-301000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-260000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-543000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>157000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>760000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1001000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-852000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7992000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>919300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>18800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>337500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>462100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>536300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>554300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>208500</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-44000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-155000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-40000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>138000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-235000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1038000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1359000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1515000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>57100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>78200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>89100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>120000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>162300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>21300</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-285000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-216000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-388000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>197000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>622000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-766000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>186000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6633000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2434300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-38300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>259300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>373000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>416300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>392000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>187200</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-285000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-216000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-388000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>197000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>622000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-766000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>107000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6942000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2748800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-38300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>259400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>373100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>416400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>392100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>187300</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1665,35 +1725,38 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-79000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-309000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>314500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>566700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>90700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>4800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>58300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>9300</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-71400</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1787,9 +1853,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
@@ -1797,95 +1866,101 @@
         <v>-31000</v>
       </c>
       <c r="E32" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-49000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-60000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-16000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-17000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-166600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>31700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>60600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>11300</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-285000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-216000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-388000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>197000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>622000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-766000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>107000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6942000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2748800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>528400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>350100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>377900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>474700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>401400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>115900</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-285000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-216000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-388000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>197000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>622000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-766000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>107000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6942000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2748800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>528400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>350100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>377900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>474700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>401400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>115900</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2073,56 +2158,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>203000</v>
+      </c>
+      <c r="E41" s="3">
         <v>198000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>332000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>287000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>440000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>981000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>349000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>495700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>485700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>587500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>274800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>199400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>226300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>183800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>170200</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2168,201 +2257,216 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>987000</v>
+      </c>
+      <c r="E43" s="3">
         <v>878000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1195000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1250000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1500000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1678000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1842000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2163500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1879300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2746900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2501400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2496400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1105100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1112400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1002000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1281000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1400000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1531000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2203000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2087000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1638000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1606000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1760700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1662400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2116000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>721800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>708500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>684400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>696400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>699900</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E45" s="3">
         <v>60000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>30000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>62000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>37000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1243800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6370400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2034100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>246200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>270500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>269800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>278500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>275900</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>2708000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2775000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3354000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4052000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4352000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4628000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4110000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5958500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10725700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7484500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2493500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2426600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2285600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2271100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2148000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2375,23 +2479,23 @@
       <c r="F47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H47" s="3">
         <v>3000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2000</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2408,105 +2512,114 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>1662000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1623000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1727000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1762000</v>
       </c>
       <c r="G48" s="3">
         <v>1762000</v>
       </c>
       <c r="H48" s="3">
+        <v>1762000</v>
+      </c>
+      <c r="I48" s="3">
         <v>1706000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1770000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1226100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>972400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1543400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1198400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1118200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>539600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>560200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>551400</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>4735000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5046000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5559000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5947000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6874000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7117000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8625000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10024500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17072600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>24330700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4918600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4320400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2975600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3024300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3032100</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>785000</v>
+      </c>
+      <c r="E52" s="3">
         <v>754000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>717000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>691000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>464000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>404000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>359000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>330000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4220000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>478900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>311900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>262200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>268900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>366400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>429400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>10715000</v>
+      </c>
+      <c r="E54" s="3">
         <v>11004000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12163000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13262000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14269000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14700000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15642000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17722400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33135500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>33837500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7221000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6681100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6069700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6222000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6160900</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>931000</v>
+      </c>
+      <c r="E57" s="3">
         <v>891000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1003000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1062000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1680000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1526000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1102000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1191600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1226800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1518900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>642400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>674100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>558900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>527400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>468500</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E58" s="3">
         <v>197000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>451000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>742000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>125000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>595000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>465000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>318700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>661800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>601900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>394700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>397400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>174800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>211900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>367500</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E59" s="3">
         <v>88000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>89000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>53000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>59000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>102000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>131000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>458300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1909500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2171200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>957400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>819200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>870800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>831500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>824900</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2525000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2437000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2897000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3078000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3317000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3621000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2978000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3303500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4907700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4292000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1988600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1890700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1604500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1570800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1660900</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>5172000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4990000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5144000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5359000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5424000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5715000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5932000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6696300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9889200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11290900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2669100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2084500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1661600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1706500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1809300</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>483000</v>
+        <v>503000</v>
       </c>
       <c r="E62" s="3">
+        <v>504000</v>
+      </c>
+      <c r="F62" s="3">
         <v>576000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>589000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>657000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>679000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>728000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>981200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1150400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6870200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>736900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>851000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>728600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>944500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>838100</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>8324000</v>
+      </c>
+      <c r="E66" s="3">
         <v>8253000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9051000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9743000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10111000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10800000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10646000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12469200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18954200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22488700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5398100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4829700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3998200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4225300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4311800</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-3227000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2942000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2726000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2338000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2535000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3174000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2404000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2511300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4611200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2289900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2090900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2111200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2242100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2294900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2097300</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>2391000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2751000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3112000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3519000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4158000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3874000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4963000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5218400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14144700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11348800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1822900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1851400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2071500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1996700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1849100</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-285000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-216000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-388000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>197000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>622000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-766000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>107000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6942000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2748800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>528400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>350100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>377900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>474700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>401400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>115900</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>186000</v>
+      </c>
+      <c r="E83" s="3">
         <v>188000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>225000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>196000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>205000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>254000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>183000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>196200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>437200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>171600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>156100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>158900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>163700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>161600</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E89" s="3">
         <v>496000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>930000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-272000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>884000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1432000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1044000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>680000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>966200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1840400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>592900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>634100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>605200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>618500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>561300</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-247000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-259000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-284000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-312000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-289000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-259000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-265000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-384000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-406200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-441400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-211400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-161900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-138200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-177200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-222900</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-164000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-151000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-199000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>343000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-268000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-228000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>736000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4807000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1078500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8824800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-649900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-751900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>53400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-163000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-206400</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E96" s="3">
         <v>118000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>184000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>385000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>394000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>392000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>391000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>435000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>428600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-328600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-206300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-182500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-174100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-125900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-84900</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-451000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-664000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-232000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1143000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-559000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1904000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5454000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2195800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7328500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>145200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>119000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-613500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-446000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-324600</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-36000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-13000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-17000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>5000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-23000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>49300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-31400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-12800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-28100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-142000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>58000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-174000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-544000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>650000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-125000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-101800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>312700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>75400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-26900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>42500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>13600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>30600</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
